--- a/data/trans_dic/P39A1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,12; 76,37</t>
+          <t>68,56; 76,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,24; 72,16</t>
+          <t>64,52; 72,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,64; 73,27</t>
+          <t>67,67; 73,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,93; 76,66</t>
+          <t>68,21; 76,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,96; 66,44</t>
+          <t>57,86; 66,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,51; 70,88</t>
+          <t>64,64; 70,83</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,87; 92,73</t>
+          <t>67,07; 92,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,74; 71,78</t>
+          <t>59,09; 71,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,45; 90,0</t>
+          <t>66,24; 90,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,81; 74,88</t>
+          <t>67,98; 74,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,26; 87,16</t>
+          <t>66,22; 86,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,04; 83,34</t>
+          <t>68,98; 80,93</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,72; 75,29</t>
+          <t>66,03; 75,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,99; 68,33</t>
+          <t>44,82; 68,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,5; 69,49</t>
+          <t>51,63; 69,46</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61,74; 82,83</t>
+          <t>62,64; 83,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,08; 77,36</t>
+          <t>71,14; 77,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,35; 77,42</t>
+          <t>70,92; 77,27</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,89; 80,55</t>
+          <t>70,99; 80,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,84; 74,87</t>
+          <t>64,56; 74,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,17; 74,99</t>
+          <t>68,31; 74,79</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>328234; 368006</t>
+          <t>330373; 368864</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>272682; 306294</t>
+          <t>273881; 306637</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613056; 664119</t>
+          <t>613285; 665566</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>296410; 334517</t>
+          <t>297625; 334602</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>208328; 238806</t>
+          <t>207991; 239350</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513373; 564099</t>
+          <t>514396; 563703</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>428258; 593826</t>
+          <t>429545; 590746</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88981; 108737</t>
+          <t>89511; 107980</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>526183; 712685</t>
+          <t>524511; 718409</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>647647; 715100</t>
+          <t>649239; 714314</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>613519; 807025</t>
+          <t>613114; 799204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1298536; 1567617</t>
+          <t>1297395; 1522316</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>268009; 307039</t>
+          <t>269288; 307287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>297909; 484712</t>
+          <t>317941; 486064</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>575327; 776337</t>
+          <t>576834; 776041</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>123873; 166182</t>
+          <t>125678; 167110</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>466418; 507604</t>
+          <t>466787; 506534</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>602766; 663310</t>
+          <t>607663; 662047</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2213297; 2514845</t>
+          <t>2216357; 2525728</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2092459; 2415855</t>
+          <t>2083283; 2404720</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4328330; 4760952</t>
+          <t>4337062; 4748601</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,56; 76,55</t>
+          <t>68,62; 76,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,52; 72,24</t>
+          <t>63,81; 71,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,67; 73,43</t>
+          <t>67,39; 73,09</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,21; 76,68</t>
+          <t>69,11; 77,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,86; 66,59</t>
+          <t>57,95; 66,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,64; 70,83</t>
+          <t>64,97; 71,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,07; 92,25</t>
+          <t>63,05; 72,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,09; 71,28</t>
+          <t>59,39; 71,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,24; 90,72</t>
+          <t>63,04; 70,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,98; 74,79</t>
+          <t>68,14; 74,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,22; 86,32</t>
+          <t>63,83; 69,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,98; 80,93</t>
+          <t>66,97; 71,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,03; 75,35</t>
+          <t>65,61; 74,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44,82; 68,52</t>
+          <t>65,22; 70,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,63; 69,46</t>
+          <t>66,13; 71,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,64; 83,29</t>
+          <t>63,99; 83,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,14; 77,2</t>
+          <t>71,63; 77,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,92; 77,27</t>
+          <t>71,84; 78,05</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,99; 80,9</t>
+          <t>69,31; 72,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,56; 74,52</t>
+          <t>66,76; 69,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,31; 74,79</t>
+          <t>68,56; 70,82</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>349034</t>
+          <t>382173</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>290229</t>
+          <t>313544</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>639263</t>
+          <t>695716</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>330373; 368864</t>
+          <t>360629; 403527</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>273881; 306637</t>
+          <t>295659; 330059</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613285; 665566</t>
+          <t>666421; 722738</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>316623</t>
+          <t>340405</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224223</t>
+          <t>245797</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>540846</t>
+          <t>586202</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>297625; 334602</t>
+          <t>321447; 359797</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>207991; 239350</t>
+          <t>229545; 262853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514396; 563703</t>
+          <t>559542; 612542</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>515405</t>
+          <t>294696</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>98508</t>
+          <t>111494</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613913</t>
+          <t>406190</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>429545; 590746</t>
+          <t>274904; 314314</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89511; 107980</t>
+          <t>101347; 121417</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524511; 718409</t>
+          <t>382427; 426571</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>683923</t>
+          <t>738708</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>690498</t>
+          <t>534467</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1374420</t>
+          <t>1273175</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>649239; 714314</t>
+          <t>707214; 768453</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>613114; 799204</t>
+          <t>512219; 556886</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1297395; 1522316</t>
+          <t>1232499; 1309884</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>288760</t>
+          <t>329861</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>431973</t>
+          <t>485897</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>720733</t>
+          <t>815759</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>269288; 307287</t>
+          <t>308540; 351213</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>317941; 486064</t>
+          <t>465556; 506616</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>576834; 776041</t>
+          <t>782960; 844552</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>148032</t>
+          <t>147779</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>487462</t>
+          <t>545244</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>635494</t>
+          <t>693023</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>125678; 167110</t>
+          <t>125489; 163530</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>466787; 506534</t>
+          <t>522722; 566795</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>607663; 662047</t>
+          <t>665214; 722667</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2301776</t>
+          <t>2233622</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2222894</t>
+          <t>2236442</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4524669</t>
+          <t>4470064</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2216357; 2525728</t>
+          <t>2169991; 2279618</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2083283; 2404720</t>
+          <t>2187137; 2285944</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4337062; 4748601</t>
+          <t>4392502; 4537611</t>
         </is>
       </c>
     </row>
